--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0105.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0105.xlsx
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Sao, thất vọng vì ta vẫn còn sống à?</t>
+          <t>Sao, thất vọng vì tao vẫn còn sống à?</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Ngươi *lời nguyền Liên bang mới*... Ta vừa tổ chức tang lễ cho ngươi hôm qua thôi!</t>
+          <t>Mày *lời nguyền Liên bang mới*... Tao vừa tổ chức tang lễ cho mày hôm qua thôi!</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Ừ. Nhưng... đó là giới hạn của tụi ta rồi.</t>
+          <t>Ừ. Nhưng... đó là giới hạn của tụi tao rồi.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Tiền bối xem đoạn dữ liệu này chưa?</t>
+          <t>bạn xem đoạn dữ liệu này chưa?</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Tiền bối xem đoạn dữ liệu này chưa?</t>
+          <t>bạn xem đoạn dữ liệu này chưa?</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Không, chúng ta sẽ giải quyết chuyện này. Nhưng trước hết phải nói chuyện với Roya ở Rừng Bjartr đã. Không thể gộp tất cả lại rồi đàn áp bừa...</t>
+          <t>Không, chúng ta sẽ giải quyết chuyện này. Nhưng trước hết phải nói chuyện với Roya ở Bjartr Woods đã. Không thể gộp tất cả lại rồi đàn áp bừa...</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Ôi trời... thôi đi! Nếu cậu muốn kiểm tra xem có phải đang mơ không, tự đấm mình đi!</t>
+          <t>Ôi trời... thôi đi! Nếu mày muốn kiểm tra xem có phải đang mơ không, tự đấm mình đi!</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Cái quái gì thế này?! Gửi cho ta tấm ảnh chữ Royan, bảo "Chăm sóc gia đình ta giùm", rồi biến mất luôn. Ta phải nghĩ sao đây?!</t>
+          <t>Cái quái gì thế này?! Gửi cho tao tấm ảnh chữ Royan, bảo "Chăm sóc gia đình tao giùm", rồi biến mất luôn. Tao phải nghĩ sao đây?!</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Muốn gãy chân à?! "Tín hiệu kém" cái con khỉ. Chỗ đó chẳng phải nhà thứ hai của cậu à? Cậu đã lái xe đến đó bao nhiêu lần rồi?</t>
+          <t>Muốn gãy chân à?! "Tín hiệu kém" cái con khỉ. Chỗ đó chẳng phải nhà thứ hai của mày à? Mày đã lái xe đến đó bao nhiêu lần rồi?</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>...May mà chính ta là người đã độ xe cho ngươi.</t>
+          <t>...May mà chính tao là người đã độ xe cho mày.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Ừm... Ừm... Hay là cậu thử cắn một miếng xem sao?</t>
+          <t>Ừm... Ừm... Hay là bạn thử cắn một miếng xem sao?</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Cậu điên à? Nếu cố vấn bắt được cậu nghịch thiết bị lần nữa, thì quên luôn chuyện tốt nghiệp đi nhé.</t>
+          <t>Mày điên à? Nếu cố vấn bắt được mày nghịch thiết bị lần nữa, thì quên luôn chuyện tốt nghiệp đi nhé.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Cậu vừa nói cái gì?</t>
+          <t>Mày vừa nói cái gì?</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Ừ. Mỗi lần tụi ta đi qua, nó vẫn ở đó. Không thấy nó bây giờ cảm giác thật lạ...</t>
+          <t>Ừ. Mỗi lần tụi tao đi qua, nó vẫn ở đó. Không thấy nó bây giờ cảm giác thật lạ...</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Ta không sao. Bão Hư Không không còn nữa. Từ giờ sẽ thuận buồm xuôi gió thôi.</t>
+          <t>Tao không sao. Bão Hư Không không còn nữa. Từ giờ sẽ thuận buồm xuôi gió thôi.</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Nghe nói Bờ Biển Đen đã giúp đỡ. Khiến ta tự hỏi liệu cái gọi là "Hệ thống Tethys" của bọn họ có thể vượt mặt được ta không.</t>
+          <t>Nghe nói Bờ Biển Đen đã giúp đỡ. Khiến tao tự hỏi liệu cái gọi là "Hệ thống Tethys" của bọn họ có thể vượt mặt được tao không.</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Trừ khi ta chết! Dù là Bão Hư Không đi nữa, những kẻ ích kỷ như thế chỉ là mối nguy hiểm biết đi!</t>
+          <t>Trừ khi tao chết! Dù là Bão Hư Không đi nữa, những kẻ ích kỷ như thế chỉ là mối nguy hiểm biết đi!</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Của ta à? Ta lái xe thẳng lên trời sửa Helios đấy! Thế nào?!</t>
+          <t>Của tao à? Tao lái xe thẳng lên trời sửa Helios đấy! Thế nào?!</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Ta đã đoán là một con khỉ to xác sẽ xuất hiện mà.</t>
+          <t>Tao đã đoán là một con khỉ to xác sẽ xuất hiện mà.</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>("Một đường đua bí mật. Đúng như ta đoán.")</t>
+          <t>("Một đường đua bí mật. Đúng như tao đoán.")</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>(Nếu dính mấy đoàn tàu này, ta tiêu đời. Tốt nhất là nhảy sang đường ray khác né chúng.)</t>
+          <t>(Nếu dính mấy đoàn tàu này, tao tiêu đời. Tốt nhất là nhảy sang đường ray khác né chúng.)</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Haha. Đúng như ta nói, ngươi có đôi mắt của Tay Đua Số Một Lahai-Roi đấy!</t>
+          <t>Haha. Đúng như tao nói, mày có đôi mắt của Tay Đua Số Một Lahai-Roi đấy!</t>
         </is>
       </c>
     </row>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Được rồi, ta thấy cái nhìn "ta có câu hỏi đây" của cậu rồi. Hỏi đi!</t>
+          <t>Được rồi, tao thấy cái nhìn "tao có câu hỏi đây" của cậu rồi. Hỏi đi!</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Hồi nhỏ, ta từng nghe tiếng gầm của nó. Suýt thủng màng nhĩ luôn. Ta vội chui tọt xuống gầm giường. Rồi tiếng bước chân rung chuyển mặt đất, càng lúc càng gần.</t>
+          <t>Hồi nhỏ, tao từng nghe tiếng gầm của nó. Suýt thủng màng nhĩ luôn. Tao vội chui tọt xuống gầm giường. Rồi tiếng bước chân rung chuyển mặt đất, càng lúc càng gần.</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Để trả lời câu hỏi của cậu: Ta đang trên đường đến trường đua tiếp theo rồi!</t>
+          <t>Để trả lời câu hỏi của cậu: Tao đang trên đường đến trường đua tiếp theo rồi!</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Tuyệt vời. À, dù xem bao nhiêu lần đi nữa, thấy Cỗ Máy Xây Đường làm việc vẫn khiến ta phấn khích không thôi.</t>
+          <t>Tuyệt vời. À, dù xem bao nhiêu lần đi nữa, thấy Cỗ Máy Xây Đường làm việc vẫn khiến tao phấn khích không thôi.</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Ta trông cậy vào cậu lấy lại Purified Mechanite và Refined Compressed Bedrock cho ta!</t>
+          <t>Tao trông cậy vào cậu lấy lại Purified Mechanite và Refined Compressed Bedrock cho tao!</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Ta không sao. Cảm ơn đã quan tâm. Đây là tất cả những gì cậu cần.</t>
+          <t>Tao không sao. Cảm ơn đã quan tâm. Đây là tất cả những gì cậu cần.</t>
         </is>
       </c>
     </row>
